--- a/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
+++ b/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850A8D6A-5547-E74D-B97B-AF608B19E16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA5BE2-294B-864C-9917-E74781286D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="500" windowWidth="22000" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -248,9 +248,6 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -372,13 +369,19 @@
   </si>
   <si>
     <t>a8:h34</t>
+  </si>
+  <si>
+    <t>Designed specifically for HiRide Sterra fork system: 20mm of true hydraulic travel </t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -408,6 +411,11 @@
       <name val="Futura"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -429,12 +437,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -750,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -774,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -782,9 +791,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -798,25 +809,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -825,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1">
         <v>480</v>
@@ -849,10 +860,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -867,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1">
         <v>528</v>
@@ -891,10 +902,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -909,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1">
         <v>115</v>
@@ -936,7 +947,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1">
         <v>70</v>
@@ -963,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1">
         <v>74.5</v>
@@ -990,7 +1001,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="1">
         <v>47</v>
@@ -1011,22 +1022,22 @@
         <v>47</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1034,7 +1045,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="1">
         <v>430</v>
@@ -1058,10 +1069,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="1">
         <v>613</v>
@@ -1088,7 +1099,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="1">
         <v>1034</v>
@@ -1115,7 +1126,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="1">
         <v>68</v>
@@ -1142,7 +1153,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1">
         <v>435</v>
@@ -1169,7 +1180,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1">
         <v>568</v>
@@ -1196,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1">
         <v>374</v>
@@ -1232,7 +1243,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1532,7 +1543,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -1548,7 +1559,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -1564,7 +1575,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -1637,8 +1648,8 @@
       <c r="A46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>72</v>
+      <c r="B46" s="1">
+        <v>20</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -1710,7 +1721,7 @@
         <v>42</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -1756,7 +1767,7 @@
         <v>45</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -2046,7 +2057,7 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>

--- a/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
+++ b/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA5BE2-294B-864C-9917-E74781286D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C3D079-153A-9B42-AB4B-8AB11343E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="500" windowWidth="22000" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://usa.cinelli-milano.com/cdn/shop/collections/gamma24__0014_nemotig_1200x.jpg?v=1709885529</t>
   </si>
 </sst>
 </file>
@@ -786,6 +789,11 @@
         <v>110</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
+++ b/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C3D079-153A-9B42-AB4B-8AB11343E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC59A38-46EC-4247-A361-9B6654A5EB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="500" windowWidth="22000" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -329,9 +329,6 @@
     <t>top_tube_actual_length</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>braze on</t>
   </si>
   <si>
@@ -378,6 +375,15 @@
   </si>
   <si>
     <t>https://usa.cinelli-milano.com/cdn/shop/collections/gamma24__0014_nemotig_1200x.jpg?v=1709885529</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Milan, Italy</t>
   </si>
 </sst>
 </file>
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -762,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -786,12 +792,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -799,10 +805,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -835,7 +841,7 @@
         <v>79</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1030,22 +1036,22 @@
         <v>47</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1551,7 +1557,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -1567,7 +1573,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -1729,7 +1735,7 @@
         <v>42</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -1775,7 +1781,7 @@
         <v>45</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -2065,7 +2071,7 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2076,6 +2082,14 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
+++ b/data/gravel/Cinelli Nemo Tig 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC59A38-46EC-4247-A361-9B6654A5EB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E531810-8C67-D444-B07E-197384BD0302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="500" windowWidth="22000" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,24 @@
   </si>
   <si>
     <t>Milan, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -749,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1732,11 +1750,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1748,7 +1764,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1762,11 +1778,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>27.2</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1778,11 +1792,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1794,7 +1806,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1808,7 +1820,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1822,10 +1834,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="1">
-        <v>160</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1838,11 +1850,9 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="1">
-        <v>160</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -1854,9 +1864,11 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1868,9 +1880,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1882,7 +1896,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1896,7 +1910,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1910,9 +1924,11 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B63" s="1">
+        <v>160</v>
+      </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -1924,9 +1940,11 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B64" s="1">
+        <v>160</v>
+      </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -1938,7 +1956,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1952,7 +1970,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1966,7 +1984,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1980,7 +1998,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1994,7 +2012,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2008,7 +2026,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2022,11 +2040,9 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3990</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2038,11 +2054,9 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1">
-        <v>5490</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2054,7 +2068,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2068,11 +2082,9 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -2083,10 +2095,100 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3990</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>5490</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>115</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>116</v>
       </c>
     </row>
